--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_DE MORRO FINO CANTBASKET04.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_DE MORRO FINO CANTBASKET04.xlsx
@@ -565,13 +565,13 @@
         <v>22</v>
       </c>
       <c r="D2" t="n">
-        <v>34.7865</v>
+        <v>38.9241</v>
       </c>
       <c r="E2" t="n">
-        <v>38.173</v>
+        <v>42.8241</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.3863</v>
+        <v>-3.8998</v>
       </c>
       <c r="G2" t="n">
         <v>29.0385</v>
@@ -610,13 +610,13 @@
         <v>48.4451</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.8683</v>
+        <v>2.269400000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>-3.5423</v>
+        <v>1.1089</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6738</v>
+        <v>1.1603</v>
       </c>
       <c r="V2" t="n">
         <v>7.4238</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. CARPINTERO REVILLA</t>
+          <t>J. JORGE RODRIGUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>28.4542</v>
+        <v>31.5597</v>
       </c>
       <c r="E3" t="n">
-        <v>28.6285</v>
+        <v>44.7134</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1745000000000009</v>
+        <v>-13.1537</v>
       </c>
       <c r="G3" t="n">
-        <v>5.0223</v>
+        <v>33.453</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.7704000000000013</v>
+        <v>4.8441</v>
       </c>
       <c r="I3" t="n">
-        <v>5.7925</v>
+        <v>28.609</v>
       </c>
       <c r="J3" t="n">
-        <v>32.4312</v>
+        <v>74.2141</v>
       </c>
       <c r="K3" t="n">
-        <v>21.9259</v>
+        <v>37.1245</v>
       </c>
       <c r="L3" t="n">
-        <v>10.5059</v>
+        <v>37.0895</v>
       </c>
       <c r="M3" t="n">
-        <v>-27.409</v>
+        <v>-40.7608</v>
       </c>
       <c r="N3" t="n">
-        <v>-22.6964</v>
+        <v>-32.2806</v>
       </c>
       <c r="O3" t="n">
-        <v>-4.712899999999999</v>
+        <v>-8.480300000000002</v>
       </c>
       <c r="P3" t="n">
-        <v>1.544</v>
+        <v>-10.8082</v>
       </c>
       <c r="Q3" t="n">
-        <v>-38.7942</v>
+        <v>-68.51779999999999</v>
       </c>
       <c r="R3" t="n">
-        <v>40.3388</v>
+        <v>57.7092</v>
       </c>
       <c r="S3" t="n">
-        <v>22.7455</v>
+        <v>-9.082799999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>25.2201</v>
+        <v>-2.7238</v>
       </c>
       <c r="U3" t="n">
-        <v>-2.475</v>
+        <v>-6.3592</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.8579000000000001</v>
+        <v>17.998</v>
       </c>
       <c r="W3" t="n">
-        <v>9.771699999999999</v>
+        <v>41.7412</v>
       </c>
       <c r="X3" t="n">
-        <v>-10.6297</v>
+        <v>-23.7432</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. HERNANDEZ HERNANDEZ</t>
+          <t>E. CARPINTERO REVILLA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>14.6583</v>
+        <v>14.7656</v>
       </c>
       <c r="E4" t="n">
-        <v>8.2966</v>
+        <v>12.9354</v>
       </c>
       <c r="F4" t="n">
-        <v>6.3618</v>
+        <v>1.8298</v>
       </c>
       <c r="G4" t="n">
-        <v>-7.770000000000001</v>
+        <v>5.0223</v>
       </c>
       <c r="H4" t="n">
-        <v>-8.0444</v>
+        <v>-0.7704000000000013</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2743999999999999</v>
+        <v>5.7925</v>
       </c>
       <c r="J4" t="n">
-        <v>18.5557</v>
+        <v>32.4312</v>
       </c>
       <c r="K4" t="n">
-        <v>10.7579</v>
+        <v>21.9259</v>
       </c>
       <c r="L4" t="n">
-        <v>7.798</v>
+        <v>10.5059</v>
       </c>
       <c r="M4" t="n">
-        <v>-26.3254</v>
+        <v>-27.409</v>
       </c>
       <c r="N4" t="n">
-        <v>-18.8024</v>
+        <v>-22.6964</v>
       </c>
       <c r="O4" t="n">
-        <v>-7.523499999999999</v>
+        <v>-4.712899999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>-8.4924</v>
+        <v>1.544</v>
       </c>
       <c r="Q4" t="n">
-        <v>-42.6545</v>
+        <v>-38.7942</v>
       </c>
       <c r="R4" t="n">
-        <v>34.1625</v>
+        <v>40.3388</v>
       </c>
       <c r="S4" t="n">
-        <v>31.6706</v>
+        <v>9.0564</v>
       </c>
       <c r="T4" t="n">
-        <v>22.4229</v>
+        <v>9.526899999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>9.247400000000001</v>
+        <v>-0.4703000000000002</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.75</v>
+        <v>-0.8579000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>9.973100000000001</v>
+        <v>9.771699999999999</v>
       </c>
       <c r="X4" t="n">
-        <v>-10.7228</v>
+        <v>-10.6297</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. KEITH CAMARA</t>
+          <t>F. AMBROSONI ÁLVAREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>7.4483</v>
+        <v>9.0549</v>
       </c>
       <c r="E5" t="n">
-        <v>9.156000000000001</v>
+        <v>20.3374</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.7078</v>
+        <v>-11.2827</v>
       </c>
       <c r="G5" t="n">
-        <v>1.463300000000001</v>
+        <v>14.9867</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5709000000000001</v>
+        <v>2.5999</v>
       </c>
       <c r="I5" t="n">
-        <v>2.0341</v>
+        <v>12.387</v>
       </c>
       <c r="J5" t="n">
-        <v>7.7606</v>
+        <v>51.0021</v>
       </c>
       <c r="K5" t="n">
-        <v>5.1332</v>
+        <v>27.9554</v>
       </c>
       <c r="L5" t="n">
-        <v>2.6278</v>
+        <v>23.0472</v>
       </c>
       <c r="M5" t="n">
-        <v>-6.2974</v>
+        <v>-36.0154</v>
       </c>
       <c r="N5" t="n">
-        <v>-5.7038</v>
+        <v>-25.3551</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5934</v>
+        <v>-10.66</v>
       </c>
       <c r="P5" t="n">
-        <v>4.6321</v>
+        <v>-21.4237</v>
       </c>
       <c r="Q5" t="n">
-        <v>-5.2111</v>
+        <v>-69.09690000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>9.843299999999999</v>
+        <v>47.6731</v>
       </c>
       <c r="S5" t="n">
-        <v>2.8244</v>
+        <v>-5.428599999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>4.8071</v>
+        <v>-3.0978</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.9825</v>
+        <v>-2.3306</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.4717</v>
+        <v>20.9202</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7997</v>
+        <v>41.5301</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.2715</v>
+        <v>-20.6098</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. JORGE RODRIGUEZ</t>
+          <t>D. KEITH CAMARA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>6.7973</v>
+        <v>5.510899999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>26.7438</v>
+        <v>6.6306</v>
       </c>
       <c r="F6" t="n">
-        <v>-19.9465</v>
+        <v>-1.1197</v>
       </c>
       <c r="G6" t="n">
-        <v>33.453</v>
+        <v>1.463300000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>4.8441</v>
+        <v>-0.5709000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>28.609</v>
+        <v>2.0341</v>
       </c>
       <c r="J6" t="n">
-        <v>74.2141</v>
+        <v>7.7606</v>
       </c>
       <c r="K6" t="n">
-        <v>37.1245</v>
+        <v>5.1332</v>
       </c>
       <c r="L6" t="n">
-        <v>37.0895</v>
+        <v>2.6278</v>
       </c>
       <c r="M6" t="n">
-        <v>-40.7608</v>
+        <v>-6.2974</v>
       </c>
       <c r="N6" t="n">
-        <v>-32.2806</v>
+        <v>-5.7038</v>
       </c>
       <c r="O6" t="n">
-        <v>-8.480300000000002</v>
+        <v>-0.5934</v>
       </c>
       <c r="P6" t="n">
-        <v>-10.8082</v>
+        <v>4.6321</v>
       </c>
       <c r="Q6" t="n">
-        <v>-68.51779999999999</v>
+        <v>-5.2111</v>
       </c>
       <c r="R6" t="n">
-        <v>57.7092</v>
+        <v>9.843299999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>-33.8453</v>
+        <v>0.8871</v>
       </c>
       <c r="T6" t="n">
-        <v>-20.6931</v>
+        <v>2.2815</v>
       </c>
       <c r="U6" t="n">
-        <v>-13.1521</v>
+        <v>-1.3947</v>
       </c>
       <c r="V6" t="n">
-        <v>17.998</v>
+        <v>-1.4717</v>
       </c>
       <c r="W6" t="n">
-        <v>41.7412</v>
+        <v>1.7997</v>
       </c>
       <c r="X6" t="n">
-        <v>-23.7432</v>
+        <v>-3.2715</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7675000000000001</v>
+        <v>5.2624</v>
       </c>
       <c r="E7" t="n">
-        <v>1.793</v>
+        <v>4.1745</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0258</v>
+        <v>1.087400000000001</v>
       </c>
       <c r="G7" t="n">
         <v>1.5805</v>
@@ -1000,13 +1000,13 @@
         <v>7.9131</v>
       </c>
       <c r="S7" t="n">
-        <v>-4.2963</v>
+        <v>0.1983</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.3774</v>
+        <v>1.0042</v>
       </c>
       <c r="U7" t="n">
-        <v>-2.9189</v>
+        <v>-0.806</v>
       </c>
       <c r="V7" t="n">
         <v>-0.5697000000000001</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ MARTIN</t>
+          <t>D. LAMAZARES ABASCAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1514</v>
+        <v>0.7736000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.4452000000000002</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1514</v>
+        <v>0.3283999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1335</v>
+        <v>1.4592</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.7702</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1335</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1.4653</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.2782</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.1871</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1335</v>
+        <v>-0.005999999999999978</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-0.508</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1335</v>
+        <v>0.5019</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.544</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.509</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0178</v>
+        <v>-0.7159</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.6012</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0178</v>
+        <v>-1.3171</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.5139</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.8576999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. LAMAZARES ABASCAL</t>
+          <t>A. RODRIGUEZ MARTIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4875000000000001</v>
+        <v>0.1781</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5752000000000002</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.08739999999999992</v>
+        <v>0.1781</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4592</v>
+        <v>0.1335</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7702</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.1335</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4653</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2782</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1871</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.005999999999999978</v>
+        <v>0.1335</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.508</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5019</v>
+        <v>0.1335</v>
       </c>
       <c r="P9" t="n">
-        <v>1.544</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.509</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.977</v>
+        <v>0.0446</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4189999999999999</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.5579</v>
+        <v>0.0446</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5139</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6562</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8576999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. REYES ABAD</t>
+          <t>D. RUIZ RUIZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.908799999999998</v>
+        <v>-1.8067</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8527000000000009</v>
+        <v>-0.7651</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0563</v>
+        <v>-1.0414</v>
       </c>
       <c r="G10" t="n">
-        <v>-16.7868</v>
+        <v>-1.2066</v>
       </c>
       <c r="H10" t="n">
-        <v>-10.6755</v>
+        <v>-1.6072</v>
       </c>
       <c r="I10" t="n">
-        <v>-6.111000000000001</v>
+        <v>0.4006</v>
       </c>
       <c r="J10" t="n">
-        <v>14.2992</v>
+        <v>0.2085</v>
       </c>
       <c r="K10" t="n">
-        <v>12.9758</v>
+        <v>-0.6054999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3236</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-31.0861</v>
+        <v>-1.4151</v>
       </c>
       <c r="N10" t="n">
-        <v>-23.6514</v>
+        <v>-1.0017</v>
       </c>
       <c r="O10" t="n">
-        <v>-7.4348</v>
+        <v>-0.4134</v>
       </c>
       <c r="P10" t="n">
-        <v>9.4573</v>
+        <v>-0.579</v>
       </c>
       <c r="Q10" t="n">
-        <v>-38.2154</v>
+        <v>-1.158</v>
       </c>
       <c r="R10" t="n">
-        <v>47.6729</v>
+        <v>0.579</v>
       </c>
       <c r="S10" t="n">
-        <v>10.1586</v>
+        <v>-0.3491</v>
       </c>
       <c r="T10" t="n">
-        <v>10.508</v>
+        <v>0.1844</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3492000000000004</v>
+        <v>-0.5334</v>
       </c>
       <c r="V10" t="n">
-        <v>-4.7385</v>
+        <v>0.3281</v>
       </c>
       <c r="W10" t="n">
-        <v>12.5559</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-17.2943</v>
+        <v>0.3281</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1964</v>
+        <v>-2.2035</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6639000000000002</v>
+        <v>-0.5638000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5326</v>
+        <v>-1.6398</v>
       </c>
       <c r="G11" t="n">
         <v>-0.1367</v>
@@ -1312,13 +1312,13 @@
         <v>0.579</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.16</v>
+        <v>-0.167</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4165</v>
+        <v>-0.3163</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2564</v>
+        <v>0.1494</v>
       </c>
       <c r="V11" t="n">
         <v>-1.5139</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. RUIZ RUIZ</t>
+          <t>O. HERNANDEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5681</v>
+        <v>-3.470299999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.3661</v>
+        <v>-6.214099999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2021</v>
+        <v>2.7435</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.2066</v>
+        <v>-7.770000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.6072</v>
+        <v>-8.0444</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4006</v>
+        <v>0.2743999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2085</v>
+        <v>18.5557</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6054999999999999</v>
+        <v>10.7579</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8139999999999999</v>
+        <v>7.798</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.4151</v>
+        <v>-26.3254</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.0017</v>
+        <v>-18.8024</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4134</v>
+        <v>-7.523499999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.579</v>
+        <v>-8.4924</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.158</v>
+        <v>-42.6545</v>
       </c>
       <c r="R12" t="n">
-        <v>0.579</v>
+        <v>34.1625</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1105</v>
+        <v>13.5421</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4165</v>
+        <v>7.9124</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6941000000000001</v>
+        <v>5.6296</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3281</v>
+        <v>-0.75</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>9.973100000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>0.3281</v>
+        <v>-10.7228</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>N. NDOYE</t>
+          <t>J. PATERNINA ARBIDE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.9495</v>
+        <v>-6.4593</v>
       </c>
       <c r="E13" t="n">
-        <v>6.4468</v>
+        <v>-5.1348</v>
       </c>
       <c r="F13" t="n">
-        <v>-11.3959</v>
+        <v>-1.3245</v>
       </c>
       <c r="G13" t="n">
-        <v>-13.5505</v>
+        <v>-2.6286</v>
       </c>
       <c r="H13" t="n">
-        <v>-5.090999999999999</v>
+        <v>-1.2811</v>
       </c>
       <c r="I13" t="n">
-        <v>-8.459299999999999</v>
+        <v>-1.3474</v>
       </c>
       <c r="J13" t="n">
-        <v>6.733200000000001</v>
+        <v>2.6966</v>
       </c>
       <c r="K13" t="n">
-        <v>6.3111</v>
+        <v>2.3388</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4221999999999998</v>
+        <v>0.3577999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-20.2835</v>
+        <v>-5.325100000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-11.4023</v>
+        <v>-3.6199</v>
       </c>
       <c r="O13" t="n">
-        <v>-8.881499999999999</v>
+        <v>-1.7051</v>
       </c>
       <c r="P13" t="n">
-        <v>1.158</v>
+        <v>-3.0881</v>
       </c>
       <c r="Q13" t="n">
-        <v>-22.0026</v>
+        <v>-7.1412</v>
       </c>
       <c r="R13" t="n">
-        <v>23.1608</v>
+        <v>4.053</v>
       </c>
       <c r="S13" t="n">
-        <v>13.9944</v>
+        <v>0.03039999999999998</v>
       </c>
       <c r="T13" t="n">
-        <v>9.9338</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>4.0606</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>-6.551600000000001</v>
+        <v>-0.7732</v>
       </c>
       <c r="W13" t="n">
-        <v>11.7827</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-18.334</v>
+        <v>-0.7732</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. PATERNINA ARBIDE</t>
+          <t>A. GARCIA NAVALON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.9223</v>
+        <v>-8.3371</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.197</v>
+        <v>-11.2547</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.7251</v>
+        <v>2.9176</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.6286</v>
+        <v>-16.3396</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.2811</v>
+        <v>-22.1698</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.3474</v>
+        <v>5.8301</v>
       </c>
       <c r="J14" t="n">
-        <v>2.6966</v>
+        <v>2.2495</v>
       </c>
       <c r="K14" t="n">
-        <v>2.3388</v>
+        <v>-4.571099999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3577999999999999</v>
+        <v>6.821200000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-5.325100000000001</v>
+        <v>-18.589</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.6199</v>
+        <v>-17.5987</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.7051</v>
+        <v>-0.9905000000000002</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.0881</v>
+        <v>3.0884</v>
       </c>
       <c r="Q14" t="n">
-        <v>-7.1412</v>
+        <v>-23.5468</v>
       </c>
       <c r="R14" t="n">
-        <v>4.053</v>
+        <v>26.6349</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.4326</v>
+        <v>-3.461</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.7524</v>
+        <v>-1.5384</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3198</v>
+        <v>-1.9228</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.7732</v>
+        <v>8.3756</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>11.5814</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.7732</v>
+        <v>-3.2058</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. AMBROSONI ÁLVAREZ</t>
+          <t>A. REY GUTIERREZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>-11.0276</v>
+        <v>-8.9802</v>
       </c>
       <c r="E15" t="n">
-        <v>5.4689</v>
+        <v>-9.5624</v>
       </c>
       <c r="F15" t="n">
-        <v>-16.4965</v>
+        <v>0.5821999999999994</v>
       </c>
       <c r="G15" t="n">
-        <v>14.9867</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5999</v>
+        <v>-14.4083</v>
       </c>
       <c r="I15" t="n">
-        <v>12.387</v>
+        <v>13.5937</v>
       </c>
       <c r="J15" t="n">
-        <v>51.0021</v>
+        <v>10.6865</v>
       </c>
       <c r="K15" t="n">
-        <v>27.9554</v>
+        <v>-2.847100000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>23.0472</v>
+        <v>13.5338</v>
       </c>
       <c r="M15" t="n">
-        <v>-36.0154</v>
+        <v>-11.5013</v>
       </c>
       <c r="N15" t="n">
-        <v>-25.3551</v>
+        <v>-11.5611</v>
       </c>
       <c r="O15" t="n">
-        <v>-10.66</v>
+        <v>0.05990000000000029</v>
       </c>
       <c r="P15" t="n">
-        <v>-21.4237</v>
+        <v>-1.1581</v>
       </c>
       <c r="Q15" t="n">
-        <v>-69.09690000000001</v>
+        <v>-21.4235</v>
       </c>
       <c r="R15" t="n">
-        <v>47.6731</v>
+        <v>20.2657</v>
       </c>
       <c r="S15" t="n">
-        <v>-25.5108</v>
+        <v>1.63</v>
       </c>
       <c r="T15" t="n">
-        <v>-17.9662</v>
+        <v>-1.2809</v>
       </c>
       <c r="U15" t="n">
-        <v>-7.545</v>
+        <v>2.9107</v>
       </c>
       <c r="V15" t="n">
-        <v>20.9202</v>
+        <v>-8.637499999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>41.5301</v>
+        <v>2.456</v>
       </c>
       <c r="X15" t="n">
-        <v>-20.6098</v>
+        <v>-11.0933</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. REY GUTIERREZ</t>
+          <t>A. REYES ABAD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D16" t="n">
-        <v>-12.7518</v>
+        <v>-9.7698</v>
       </c>
       <c r="E16" t="n">
-        <v>-12.542</v>
+        <v>-8.1371</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2098000000000003</v>
+        <v>-1.6327</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8149999999999999</v>
+        <v>-16.7868</v>
       </c>
       <c r="H16" t="n">
-        <v>-14.4083</v>
+        <v>-10.6755</v>
       </c>
       <c r="I16" t="n">
-        <v>13.5937</v>
+        <v>-6.111000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>10.6865</v>
+        <v>14.2992</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.847100000000001</v>
+        <v>12.9758</v>
       </c>
       <c r="L16" t="n">
-        <v>13.5338</v>
+        <v>1.3236</v>
       </c>
       <c r="M16" t="n">
-        <v>-11.5013</v>
+        <v>-31.0861</v>
       </c>
       <c r="N16" t="n">
-        <v>-11.5611</v>
+        <v>-23.6514</v>
       </c>
       <c r="O16" t="n">
-        <v>0.05990000000000029</v>
+        <v>-7.4348</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1581</v>
+        <v>9.4573</v>
       </c>
       <c r="Q16" t="n">
-        <v>-21.4235</v>
+        <v>-38.2154</v>
       </c>
       <c r="R16" t="n">
-        <v>20.2657</v>
+        <v>47.6729</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.1416</v>
+        <v>2.2979</v>
       </c>
       <c r="T16" t="n">
-        <v>-4.2603</v>
+        <v>3.2235</v>
       </c>
       <c r="U16" t="n">
-        <v>2.1188</v>
+        <v>-0.9254</v>
       </c>
       <c r="V16" t="n">
-        <v>-8.637499999999999</v>
+        <v>-4.7385</v>
       </c>
       <c r="W16" t="n">
-        <v>2.456</v>
+        <v>12.5559</v>
       </c>
       <c r="X16" t="n">
-        <v>-11.0933</v>
+        <v>-17.2943</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. GARCIA NAVALON</t>
+          <t>N. NDOYE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>-22.8006</v>
+        <v>-13.9945</v>
       </c>
       <c r="E17" t="n">
-        <v>-20.4992</v>
+        <v>0.6949999999999998</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.3014</v>
+        <v>-14.6897</v>
       </c>
       <c r="G17" t="n">
-        <v>-16.3396</v>
+        <v>-13.5505</v>
       </c>
       <c r="H17" t="n">
-        <v>-22.1698</v>
+        <v>-5.090999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>5.8301</v>
+        <v>-8.459299999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>2.2495</v>
+        <v>6.733200000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>-4.571099999999999</v>
+        <v>6.3111</v>
       </c>
       <c r="L17" t="n">
-        <v>6.821200000000001</v>
+        <v>0.4221999999999998</v>
       </c>
       <c r="M17" t="n">
-        <v>-18.589</v>
+        <v>-20.2835</v>
       </c>
       <c r="N17" t="n">
-        <v>-17.5987</v>
+        <v>-11.4023</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9905000000000002</v>
+        <v>-8.881499999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>3.0884</v>
+        <v>1.158</v>
       </c>
       <c r="Q17" t="n">
-        <v>-23.5468</v>
+        <v>-22.0026</v>
       </c>
       <c r="R17" t="n">
-        <v>26.6349</v>
+        <v>23.1608</v>
       </c>
       <c r="S17" t="n">
-        <v>-17.9244</v>
+        <v>4.949</v>
       </c>
       <c r="T17" t="n">
-        <v>-10.7831</v>
+        <v>4.1821</v>
       </c>
       <c r="U17" t="n">
-        <v>-7.1419</v>
+        <v>0.7669000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>8.3756</v>
+        <v>-6.551600000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>11.5814</v>
+        <v>11.7827</v>
       </c>
       <c r="X17" t="n">
-        <v>-3.2058</v>
+        <v>-18.334</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>25.4509</v>
+        <v>51.00790000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>81.01049999999999</v>
+        <v>91.12360000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-55.56</v>
+        <v>-40.117</v>
       </c>
       <c r="G18" t="n">
         <v>27.9032</v>
@@ -1828,7 +1828,7 @@
         <v>-42.9984</v>
       </c>
       <c r="I18" t="n">
-        <v>70.9019</v>
+        <v>70.90190000000001</v>
       </c>
       <c r="J18" t="n">
         <v>289.1799</v>
@@ -1858,13 +1858,13 @@
         <v>371.5394</v>
       </c>
       <c r="S18" t="n">
-        <v>-9.855500000000006</v>
+        <v>15.7008</v>
       </c>
       <c r="T18" t="n">
-        <v>10.26509999999999</v>
+        <v>20.3779</v>
       </c>
       <c r="U18" t="n">
-        <v>-20.122</v>
+        <v>-4.677700000000001</v>
       </c>
       <c r="V18" t="n">
         <v>27.6678</v>
